--- a/reports/utour/众信旅游_国内游调研表_已填写.xlsx
+++ b/reports/utour/众信旅游_国内游调研表_已填写.xlsx
@@ -1035,7 +1035,7 @@
       </c>
       <c r="H11" s="45" t="inlineStr">
         <is>
-          <t>人次+0.9%（基本持平）。门店向华中/华北扩张带来的新增出发地客源，被向小团、私家团和目的地参团的分流抵消，大团占比下降</t>
+          <t>人次+1.1%（基本持平）。整体：国内游收客+40%（零售与加盟门店向华中、华北、华东扩张，五一国内游出游人次+168%；国内业务基数小）。结构：新增出发地客源被向小团、私家团和目的地参团的分流抵消，大团人次占比由约38%降至约28%</t>
         </is>
       </c>
     </row>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="H12" s="45" t="inlineStr">
         <is>
-          <t>人次+46.9%（增长）。新增门店客源偏好目的地参团；新疆、云南等“顶流”目的地热度延续</t>
+          <t>人次+46.7%（增长）。整体：国内游收客+40%（零售与加盟门店向华中、华北、华东扩张，五一国内游出游人次+168%；国内业务基数小）。结构：新增门店客源偏好目的地参团；新疆、云南等“顶流”目的地热度延续</t>
         </is>
       </c>
     </row>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="H13" s="45" t="inlineStr">
         <is>
-          <t>人次+61.8%（增长）。目的地参团与短线客群增加带动一日游</t>
+          <t>人次+63.0%（增长）。整体：国内游收客+40%（零售与加盟门店向华中、华北、华东扩张，五一国内游出游人次+168%；国内业务基数小）。结构：目的地参团与短线客群增加带动一日游</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="H14" s="45" t="inlineStr">
         <is>
-          <t>人次+70.6%（增长）。大团变小团趋势延续；五一喀纳斯、伊犁等小团线路供不应求</t>
+          <t>人次+70.7%（增长）。整体：国内游收客+40%（零售与加盟门店向华中、华北、华东扩张，五一国内游出游人次+168%；国内业务基数小）。结构：大团变小团趋势延续；五一喀纳斯、伊犁等小团线路供不应求</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="H15" s="45" t="inlineStr">
         <is>
-          <t>人次+75.6%（增长）。新疆、云南、西北小车拼团成为主流形态</t>
+          <t>人次+74.6%（增长）。整体：国内游收客+40%（零售与加盟门店向华中、华北、华东扩张，五一国内游出游人次+168%；国内业务基数小）。结构：新疆、云南、西北小车拼团成为主流形态</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="H16" s="45" t="inlineStr">
         <is>
-          <t>人次+67.9%（增长）。家庭亲子出游偏好私密成团（2026暑期行业小团、私家团、定制预订占比稳步提升）</t>
+          <t>人次+67.6%（增长）。整体：国内游收客+40%（零售与加盟门店向华中、华北、华东扩张，五一国内游出游人次+168%；国内业务基数小）。结构：家庭亲子出游偏好私密成团（2026暑期行业小团、私家团、定制预订占比稳步提升）</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="H17" s="45" t="inlineStr">
         <is>
-          <t>人次+69.6%（增长）。家庭出游私密化，同上</t>
+          <t>人次+74.6%（增长）。整体：国内游收客+40%（零售与加盟门店向华中、华北、华东扩张，五一国内游出游人次+168%；国内业务基数小）。结构：家庭出游私密化，目的地私家团与出发地私家团同步增长</t>
         </is>
       </c>
     </row>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="H18" s="45" t="inlineStr">
         <is>
-          <t>人次+100.0%（增长）。定制需求扩张（2025年国内定制旅行市场规模超1,200亿元、同比+14%；2026暑期行业定制游预订人次同比超3倍）</t>
+          <t>人次+95.5%（增长）。整体：国内游收客+40%（零售与加盟门店向华中、华北、华东扩张，五一国内游出游人次+168%；国内业务基数小）。结构：定制需求扩张（2025年国内定制旅行市场规模超1,200亿元、同比+14%；2026暑期行业定制游预订人次同比超3倍）</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="H19" s="45" t="inlineStr">
         <is>
-          <t>人次+100.0%（增长）。定制需求扩张，基数小</t>
+          <t>人次+86.2%（增长）。整体：国内游收客+40%（零售与加盟门店向华中、华北、华东扩张，五一国内游出游人次+168%；国内业务基数小）。结构：定制需求扩张，基数小</t>
         </is>
       </c>
     </row>

--- a/reports/utour/众信旅游_国内游调研表_已填写.xlsx
+++ b/reports/utour/众信旅游_国内游调研表_已填写.xlsx
@@ -1022,16 +1022,16 @@
         </is>
       </c>
       <c r="D11" s="44" t="n">
-        <v>29900</v>
+        <v>41900</v>
       </c>
       <c r="E11" s="44" t="n">
-        <v>30800</v>
+        <v>43100</v>
       </c>
       <c r="F11" s="44" t="n">
-        <v>21500</v>
+        <v>30100</v>
       </c>
       <c r="G11" s="44" t="n">
-        <v>21700</v>
+        <v>30400</v>
       </c>
       <c r="H11" s="45" t="inlineStr">
         <is>
@@ -1048,16 +1048,16 @@
         </is>
       </c>
       <c r="D12" s="44" t="n">
-        <v>13300</v>
+        <v>18600</v>
       </c>
       <c r="E12" s="44" t="n">
-        <v>16200</v>
+        <v>22700</v>
       </c>
       <c r="F12" s="44" t="n">
-        <v>11300</v>
+        <v>15800</v>
       </c>
       <c r="G12" s="44" t="n">
-        <v>16600</v>
+        <v>23200</v>
       </c>
       <c r="H12" s="45" t="inlineStr">
         <is>
@@ -1074,16 +1074,16 @@
         </is>
       </c>
       <c r="D13" s="44" t="n">
-        <v>8000</v>
+        <v>11200</v>
       </c>
       <c r="E13" s="44" t="n">
-        <v>9700</v>
+        <v>13600</v>
       </c>
       <c r="F13" s="44" t="n">
-        <v>6800</v>
+        <v>9500</v>
       </c>
       <c r="G13" s="44" t="n">
-        <v>11000</v>
+        <v>15500</v>
       </c>
       <c r="H13" s="45" t="inlineStr">
         <is>
@@ -1104,16 +1104,16 @@
         </is>
       </c>
       <c r="D14" s="44" t="n">
-        <v>4700</v>
+        <v>6500</v>
       </c>
       <c r="E14" s="44" t="n">
-        <v>7300</v>
+        <v>10200</v>
       </c>
       <c r="F14" s="44" t="n">
-        <v>5100</v>
+        <v>7100</v>
       </c>
       <c r="G14" s="44" t="n">
-        <v>8700</v>
+        <v>12200</v>
       </c>
       <c r="H14" s="45" t="inlineStr">
         <is>
@@ -1130,16 +1130,16 @@
         </is>
       </c>
       <c r="D15" s="44" t="n">
-        <v>4000</v>
+        <v>5600</v>
       </c>
       <c r="E15" s="44" t="n">
-        <v>6500</v>
+        <v>9100</v>
       </c>
       <c r="F15" s="44" t="n">
-        <v>4500</v>
+        <v>6300</v>
       </c>
       <c r="G15" s="44" t="n">
-        <v>7900</v>
+        <v>11000</v>
       </c>
       <c r="H15" s="45" t="inlineStr">
         <is>
@@ -1160,16 +1160,16 @@
         </is>
       </c>
       <c r="D16" s="44" t="n">
-        <v>2700</v>
+        <v>3700</v>
       </c>
       <c r="E16" s="44" t="n">
-        <v>4100</v>
+        <v>5700</v>
       </c>
       <c r="F16" s="44" t="n">
-        <v>2800</v>
+        <v>4000</v>
       </c>
       <c r="G16" s="44" t="n">
-        <v>4700</v>
+        <v>6600</v>
       </c>
       <c r="H16" s="45" t="inlineStr">
         <is>
@@ -1186,16 +1186,16 @@
         </is>
       </c>
       <c r="D17" s="44" t="n">
-        <v>2000</v>
+        <v>2800</v>
       </c>
       <c r="E17" s="44" t="n">
+        <v>4500</v>
+      </c>
+      <c r="F17" s="44" t="n">
         <v>3200</v>
       </c>
-      <c r="F17" s="44" t="n">
-        <v>2300</v>
-      </c>
       <c r="G17" s="44" t="n">
-        <v>3900</v>
+        <v>5500</v>
       </c>
       <c r="H17" s="45" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         </is>
       </c>
       <c r="D18" s="44" t="n">
-        <v>1300</v>
+        <v>1900</v>
       </c>
       <c r="E18" s="44" t="n">
+        <v>2800</v>
+      </c>
+      <c r="F18" s="44" t="n">
         <v>2000</v>
       </c>
-      <c r="F18" s="44" t="n">
-        <v>1400</v>
-      </c>
       <c r="G18" s="44" t="n">
-        <v>2800</v>
+        <v>3900</v>
       </c>
       <c r="H18" s="45" t="inlineStr">
         <is>
@@ -1242,16 +1242,16 @@
         </is>
       </c>
       <c r="D19" s="44" t="n">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="E19" s="44" t="n">
+        <v>1700</v>
+      </c>
+      <c r="F19" s="44" t="n">
         <v>1200</v>
       </c>
-      <c r="F19" s="44" t="n">
-        <v>800</v>
-      </c>
       <c r="G19" s="44" t="n">
-        <v>1600</v>
+        <v>2200</v>
       </c>
       <c r="H19" s="45" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="B12" s="34" t="inlineStr">
         <is>
-          <t>较低可信。全部人次的量级取决于一个假设——国内团队游占众信休闲成交额的比例（2025年取5%、2026年1–8月取7%）。该比例公司从未披露，是全表最大的不确定来源；访谈拿到真实比例后，可据此对全表人次整体重算。</t>
+          <t>较低可信。全部人次的量级取决于一个假设——国内团队游占众信休闲成交额的比例（2025年取7%、2026年1–8月取9.8%）。该比例公司从未披露，是全表最大的不确定来源；访谈拿到真实比例后，可据此对全表人次整体重算。</t>
         </is>
       </c>
     </row>
@@ -1913,11 +1913,11 @@
         </is>
       </c>
       <c r="B40" s="41" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
-          <t>公司未披露；按零售成交额约30%、批发约1%估算</t>
+          <t>公司未披露；按五一收客与门店数交叉核对取中值，约合零售成交额35%、批发2%</t>
         </is>
       </c>
     </row>
@@ -1928,11 +1928,11 @@
         </is>
       </c>
       <c r="B41" s="41" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.098</v>
       </c>
       <c r="C41" s="34" t="inlineStr">
         <is>
-          <t>五一国内游GMV+38%而同期休闲成交额下滑，占比上调</t>
+          <t>按2025年比例×1.4上调：五一国内游GMV+38%而同期休闲成交额下滑</t>
         </is>
       </c>
     </row>
